--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HOTEL 4POSTES - ÁVILA AUTÉNTICA - EL BULEVAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HOTEL 4POSTES - ÁVILA AUTÉNTICA - EL BULEVAR.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8482</v>
+        <v>1.8384</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9574</v>
+        <v>1.0045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8908</v>
+        <v>0.8339</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2222</v>
+        <v>1.2295</v>
       </c>
       <c r="H2" t="n">
-        <v>0.951</v>
+        <v>0.9637</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2796</v>
+        <v>1.3137</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2796</v>
+        <v>1.3137</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0574</v>
+        <v>-0.0842</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3286</v>
+        <v>-0.35</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1743</v>
+        <v>-0.17</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3223</v>
+        <v>-0.3092</v>
       </c>
       <c r="U2" t="n">
-        <v>0.148</v>
+        <v>0.1392</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0375</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7922</v>
+        <v>2.9365</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7547</v>
+        <v>-2.0187</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2666</v>
+        <v>-2.2729</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7118</v>
+        <v>-0.6614</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5548</v>
+        <v>-1.6115</v>
       </c>
       <c r="J3" t="n">
-        <v>0.349</v>
+        <v>0.5138</v>
       </c>
       <c r="K3" t="n">
-        <v>0.867</v>
+        <v>1.0162</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.518</v>
+        <v>-0.5024</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6156</v>
+        <v>-2.7867</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5788</v>
+        <v>-1.6776</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0368</v>
+        <v>-1.1091</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4356</v>
+        <v>3.3719</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4435</v>
+        <v>3.3964</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0245</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1318</v>
+        <v>-1.1548</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1318</v>
+        <v>-1.1548</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HORCAJO GARCIA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6393</v>
+        <v>0.6079</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2995</v>
+        <v>0.6079</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6601</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6486</v>
+        <v>0.6079</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6555</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0069</v>
+        <v>0.6079</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0018</v>
+        <v>0.6079</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0018</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6079</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6504</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6573</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0069</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2196</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0979</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1217</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>J. HORCAJO GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5999</v>
+        <v>0.5831</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5999</v>
+        <v>1.3624</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.7794</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5999</v>
+        <v>-0.6731</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.6666</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5999</v>
+        <v>-0.0066</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5999</v>
+        <v>0.0334</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.7065</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0066</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.2163</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1548</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1088</v>
+        <v>-0.1505</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1171</v>
+        <v>0.0359</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0083</v>
+        <v>-0.1864</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7216</v>
+        <v>-0.7734</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9372</v>
+        <v>-0.9873</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2156</v>
+        <v>0.214</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.7068</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0418</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6018</v>
+        <v>0.6323</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3652</v>
+        <v>-1.4802</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.979</v>
+        <v>-1.0618</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2129</v>
+        <v>0.2071</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0401</v>
+        <v>0.0554</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1728</v>
+        <v>0.1517</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5523</v>
+        <v>-1.4768</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1504</v>
+        <v>0.4166</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7028</v>
+        <v>-1.8934</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3068</v>
+        <v>-0.2945</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1361</v>
+        <v>-1.1032</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8292</v>
+        <v>0.8087</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3868</v>
+        <v>2.5515</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5071</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8797</v>
+        <v>1.9047</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6937</v>
+        <v>-2.846</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6431</v>
+        <v>-1.7499</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0452</v>
+        <v>-1.0139</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4956</v>
+        <v>-0.467</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5496</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6454</v>
+        <v>-1.6019</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5433</v>
+        <v>-0.2212</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1021</v>
+        <v>-1.3807</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2873</v>
+        <v>-2.2464</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6836</v>
+        <v>-1.5896</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6037</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0705</v>
+        <v>1.2877</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0306</v>
+        <v>1.2472</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3578</v>
+        <v>-3.5341</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.7141</v>
+        <v>-2.8368</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6437</v>
+        <v>-0.6973</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S8" t="n">
-        <v>1.202</v>
+        <v>1.1898</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4873</v>
+        <v>1.4832</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2853</v>
+        <v>-0.2934</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3604</v>
+        <v>-1.3242</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.1006</v>
+        <v>-1.0447</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9682</v>
+        <v>-2.0017</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2434</v>
+        <v>-2.1228</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2753</v>
+        <v>0.1211</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6621</v>
+        <v>-1.6769</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.427</v>
+        <v>-2.4159</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7648</v>
+        <v>0.739</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9543</v>
+        <v>-0.8861</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0343</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7078</v>
+        <v>-0.7907</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3927</v>
+        <v>-1.4487</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6849</v>
+        <v>0.6579</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4262</v>
+        <v>1.3879</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7114</v>
+        <v>0.7107</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7147</v>
+        <v>0.6772</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5319</v>
+        <v>-0.5443</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5319</v>
+        <v>-0.5443</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2063</v>
+        <v>-3.3171</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9461</v>
+        <v>-1.799</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2601</v>
+        <v>-1.5182</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.9508</v>
+        <v>-4.9924</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4927</v>
+        <v>-1.5513</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4582</v>
+        <v>-3.4411</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.1283</v>
+        <v>-3.0228</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2217</v>
+        <v>0.2592</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.35</v>
+        <v>-3.282</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8226</v>
+        <v>-1.9696</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7144</v>
+        <v>-1.8105</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2643</v>
+        <v>-0.2535</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0177</v>
+        <v>0.0028</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2466</v>
+        <v>-0.2563</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1918</v>
+        <v>-0.2133</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3915</v>
+        <v>-1.4343</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4286</v>
+        <v>-4.3779</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4153</v>
+        <v>-2.2395</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0133</v>
+        <v>-2.1384</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.756</v>
+        <v>-1.729</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8067</v>
+        <v>0.8092</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5627</v>
+        <v>-2.5382</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1654</v>
+        <v>0.2644</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1994</v>
+        <v>2.2579</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.034</v>
+        <v>-1.9935</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9214</v>
+        <v>-1.9934</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3927</v>
+        <v>-1.4487</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5447</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6126</v>
+        <v>-0.5905</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0325</v>
+        <v>-0.034</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.538</v>
+        <v>-4.551</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7593</v>
+        <v>-2.6147</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7787</v>
+        <v>-1.9363</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8145</v>
+        <v>-1.8989</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0907</v>
+        <v>-2.1337</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2762</v>
+        <v>0.2348</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3781</v>
+        <v>-0.3582</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4981</v>
+        <v>-0.4798</v>
       </c>
       <c r="L12" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4365</v>
+        <v>-1.5407</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5926</v>
+        <v>-1.6539</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1562</v>
+        <v>0.1132</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5228</v>
+        <v>-0.51</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0573</v>
+        <v>0.0465</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9177</v>
+        <v>-4.8307</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2243</v>
+        <v>-3.8567</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6934</v>
+        <v>-0.9739</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.2917</v>
+        <v>-6.2805</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.5776</v>
+        <v>-4.6112</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.714</v>
+        <v>-1.6693</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.4187</v>
+        <v>-3.2043</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.4703</v>
+        <v>-2.3783</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9484</v>
+        <v>-0.826</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.873</v>
+        <v>-3.0762</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1074</v>
+        <v>-2.2328</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.8433</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6028</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2043</v>
+        <v>-0.1735</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4211</v>
+        <v>-0.4294</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.8703</v>
+        <v>-5.7512</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.9866</v>
+        <v>-3.5712</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8837</v>
+        <v>-2.18</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.2488</v>
+        <v>-3.2629</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.2139</v>
+        <v>-2.1783</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0349</v>
+        <v>-1.0847</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8307</v>
+        <v>1.033</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8288</v>
+        <v>1.0085</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0019</v>
+        <v>0.0244</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.0796</v>
+        <v>-4.2959</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.0427</v>
+        <v>-3.1868</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0368</v>
+        <v>-1.1091</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2719</v>
+        <v>0.2749</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3448</v>
+        <v>0.3673</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0728</v>
+        <v>-0.0924</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.0926</v>
+        <v>-0.0369</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1606</v>
+        <v>-0.1032</v>
       </c>
       <c r="X14" t="n">
-        <v>0.068</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.1107</v>
+        <v>-24.1116</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.436</v>
+        <v>-10.0613</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.6745</v>
+        <v>-14.0504</v>
       </c>
       <c r="G15" t="n">
-        <v>-24.1327</v>
+        <v>-24.2635</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.1684</v>
+        <v>-16.1256</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.964499999999999</v>
+        <v>-8.138</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5520999999999987</v>
+        <v>0.8408000000000002</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9751</v>
+        <v>4.0319</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.527099999999999</v>
+        <v>-3.1914</v>
       </c>
       <c r="M15" t="n">
-        <v>-23.581</v>
+        <v>-25.1042</v>
       </c>
       <c r="N15" t="n">
-        <v>-19.1434</v>
+        <v>-20.1575</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.4373</v>
+        <v>-4.9467</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.0008</v>
+        <v>-2.921</v>
       </c>
       <c r="Q15" t="n">
-        <v>-22.0065</v>
+        <v>-21.4211</v>
       </c>
       <c r="R15" t="n">
-        <v>19.0052</v>
+        <v>18.4998</v>
       </c>
       <c r="S15" t="n">
-        <v>3.523499999999999</v>
+        <v>3.507200000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>3.924900000000001</v>
+        <v>4.061100000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4012999999999999</v>
+        <v>-0.554</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5008999999999997</v>
+        <v>-0.4342</v>
       </c>
       <c r="W15" t="n">
-        <v>6.197300000000001</v>
+        <v>6.4581</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.6981</v>
+        <v>-6.891999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HOTEL 4POSTES - ÁVILA AUTÉNTICA - EL BULEVAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HOTEL 4POSTES - ÁVILA AUTÉNTICA - EL BULEVAR.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8384</v>
+        <v>2.0154</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0045</v>
+        <v>1.1042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8339</v>
+        <v>0.9112</v>
       </c>
       <c r="G2" t="n">
         <v>1.2295</v>
@@ -610,13 +610,13 @@
         <v>0.7789</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.17</v>
+        <v>0.0069</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3092</v>
+        <v>-0.2095</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1392</v>
+        <v>0.2164</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARTIN CASTANEDA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.6079</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9365</v>
+        <v>0.6079</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0187</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2729</v>
+        <v>0.6079</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6614</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6115</v>
+        <v>0.6079</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5138</v>
+        <v>0.6079</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0162</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5024</v>
+        <v>0.6079</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.7867</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6776</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1091</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9474</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3719</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3964</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0245</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1548</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>J. HORCAJO GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6079</v>
+        <v>0.3497</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6079</v>
+        <v>1.1631</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.8134</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6079</v>
+        <v>-0.6731</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0.6666</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6079</v>
+        <v>-0.0066</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6079</v>
+        <v>0.0334</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.0334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6079</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.7065</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.0066</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.0171</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.0914</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.0743</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1548</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HORCAJO GARCIA</t>
+          <t>A. MARTIN CASTANEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5831</v>
+        <v>-0.405</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3624</v>
+        <v>1.3417</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7794</v>
+        <v>-1.7466</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6731</v>
+        <v>-2.2729</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6666</v>
+        <v>-0.6614</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0066</v>
+        <v>-1.6115</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0334</v>
+        <v>0.5138</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0334</v>
+        <v>1.0162</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.5024</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7065</v>
+        <v>-2.7867</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7</v>
+        <v>-1.6776</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0066</v>
+        <v>-1.1091</v>
       </c>
       <c r="P5" t="n">
         <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9737</v>
+        <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2163</v>
+        <v>2.0491</v>
       </c>
       <c r="T5" t="n">
-        <v>0.108</v>
+        <v>1.8016</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1083</v>
+        <v>0.2476</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06619999999999999</v>
+        <v>-1.1548</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-1.1548</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. HERNANDEZ MARTIN</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1505</v>
+        <v>-0.4684</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0359</v>
+        <v>1.3137</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1864</v>
+        <v>-1.7821</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7734</v>
+        <v>-0.2945</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9873</v>
+        <v>-1.1032</v>
       </c>
       <c r="I6" t="n">
-        <v>0.214</v>
+        <v>0.8087</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7068</v>
+        <v>2.5515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6323</v>
+        <v>1.9047</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4802</v>
+        <v>-2.846</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0618</v>
+        <v>-1.7499</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4184</v>
+        <v>-1.096</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1947</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7526</v>
+        <v>1.1684</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2071</v>
+        <v>-0.0055</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0554</v>
+        <v>0.4301</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1517</v>
+        <v>-0.4356</v>
       </c>
       <c r="V6" t="n">
         <v>0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6105</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>C. HERNANDEZ MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4768</v>
+        <v>-0.4836</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4166</v>
+        <v>-0.2632</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8934</v>
+        <v>-0.2204</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2945</v>
+        <v>-0.7734</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1032</v>
+        <v>-0.9873</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8087</v>
+        <v>0.214</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5515</v>
+        <v>0.7068</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9047</v>
+        <v>0.6323</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.846</v>
+        <v>-1.4802</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7499</v>
+        <v>-1.0618</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.096</v>
+        <v>-0.4184</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7789</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1684</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0139</v>
+        <v>-0.126</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.467</v>
+        <v>-0.2436</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.1177</v>
       </c>
       <c r="V7" t="n">
         <v>0.6105</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3311</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6019</v>
+        <v>-2.2037</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2212</v>
+        <v>-0.9019</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3807</v>
+        <v>-1.3018</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2464</v>
+        <v>-4.9924</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5896</v>
+        <v>-1.5513</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-3.4411</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2877</v>
+        <v>-3.0228</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2472</v>
+        <v>0.2592</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>-3.282</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5341</v>
+        <v>-1.9696</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8368</v>
+        <v>-1.8105</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6973</v>
+        <v>-0.1591</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7789</v>
+        <v>2.1421</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7263</v>
+        <v>2.1421</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1898</v>
+        <v>0.8599</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4832</v>
+        <v>0.8999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2934</v>
+        <v>-0.0399</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3242</v>
+        <v>-0.2133</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0447</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2795</v>
+        <v>-1.4343</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0017</v>
+        <v>-2.6373</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1228</v>
+        <v>-1.4173</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1211</v>
+        <v>-1.22</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6769</v>
+        <v>-2.2464</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4159</v>
+        <v>-1.5896</v>
       </c>
       <c r="I9" t="n">
-        <v>0.739</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8861</v>
+        <v>1.2877</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9671999999999999</v>
+        <v>1.2472</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7907</v>
+        <v>-3.5341</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4487</v>
+        <v>-2.8368</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6579</v>
+        <v>-0.6973</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1684</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7789</v>
+        <v>2.7263</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3879</v>
+        <v>0.1544</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7107</v>
+        <v>0.287</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6772</v>
+        <v>-0.1327</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5443</v>
+        <v>-1.3242</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-1.0447</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5443</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3171</v>
+        <v>-2.8008</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.799</v>
+        <v>-2.7209</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5182</v>
+        <v>-0.0799</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.9924</v>
+        <v>-1.6769</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5513</v>
+        <v>-2.4159</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4411</v>
+        <v>0.739</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0228</v>
+        <v>-0.8861</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2592</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.282</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9696</v>
+        <v>-0.7907</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8105</v>
+        <v>-1.4487</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1591</v>
+        <v>0.6579</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1421</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1421</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2535</v>
+        <v>0.5888</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0028</v>
+        <v>0.1126</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2563</v>
+        <v>0.4762</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2133</v>
+        <v>-0.5443</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4343</v>
+        <v>-0.5443</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3779</v>
+        <v>-3.5781</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2395</v>
+        <v>-2.9596</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1384</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.729</v>
+        <v>-6.2805</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8092</v>
+        <v>-4.6112</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5382</v>
+        <v>-1.6693</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2644</v>
+        <v>-3.2043</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2579</v>
+        <v>-2.3783</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9935</v>
+        <v>-0.826</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9934</v>
+        <v>-3.0762</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4487</v>
+        <v>-2.2328</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5447</v>
+        <v>-0.8433</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1684</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9474</v>
+        <v>-2.921</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7789</v>
+        <v>2.5316</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5905</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>0.7236</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.034</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.89</v>
+        <v>2.4421</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCIA</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.551</v>
+        <v>-4.0232</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6147</v>
+        <v>-1.9405</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9363</v>
+        <v>-2.0828</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8989</v>
+        <v>-1.729</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1337</v>
+        <v>0.8092</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2348</v>
+        <v>-2.5382</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3582</v>
+        <v>0.2644</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4798</v>
+        <v>2.2579</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1216</v>
+        <v>-1.9935</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5407</v>
+        <v>-1.9934</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6539</v>
+        <v>-1.4487</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1132</v>
+        <v>-0.5447</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1421</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.921</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
         <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.51</v>
+        <v>-0.2358</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5565</v>
+        <v>-0.2575</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0465</v>
+        <v>0.0217</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2211</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>M. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8307</v>
+        <v>-4.1075</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8567</v>
+        <v>-2.4153</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9739</v>
+        <v>-1.6921</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.2805</v>
+        <v>-1.8989</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.6112</v>
+        <v>-2.1337</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6693</v>
+        <v>0.2348</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.2043</v>
+        <v>-0.3582</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.3783</v>
+        <v>-0.4798</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.826</v>
+        <v>0.1216</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.0762</v>
+        <v>-1.5407</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2328</v>
+        <v>-1.6539</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8433</v>
+        <v>0.1132</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3895</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.921</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5316</v>
+        <v>0.7789</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6028</v>
+        <v>-0.0665</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1735</v>
+        <v>-0.3572</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4294</v>
+        <v>0.2907</v>
       </c>
       <c r="V13" t="n">
-        <v>2.4421</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4421</v>
+        <v>1.2211</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.7512</v>
+        <v>-5.0481</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.5712</v>
+        <v>-2.9732</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.18</v>
+        <v>-2.0749</v>
       </c>
       <c r="G14" t="n">
         <v>-3.2629</v>
@@ -1546,13 +1546,13 @@
         <v>2.1421</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2749</v>
+        <v>0.9781</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3673</v>
+        <v>0.9654</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0924</v>
+        <v>0.0127</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0369</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.1116</v>
+        <v>-22.7827</v>
       </c>
       <c r="E15" t="n">
         <v>-10.0613</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.0504</v>
+        <v>-12.7212</v>
       </c>
       <c r="G15" t="n">
         <v>-24.2635</v>
@@ -1597,10 +1597,10 @@
         <v>-8.138</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8408000000000002</v>
+        <v>0.8408000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>4.0319</v>
+        <v>4.031899999999999</v>
       </c>
       <c r="L15" t="n">
         <v>-3.1914</v>
@@ -1624,16 +1624,16 @@
         <v>18.4998</v>
       </c>
       <c r="S15" t="n">
-        <v>3.507200000000001</v>
+        <v>4.835999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>4.061100000000001</v>
+        <v>4.061</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.554</v>
+        <v>0.7752000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4342</v>
+        <v>-0.4342000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>6.4581</v>
